--- a/results/final_0624_summary/scene_BinaryVector_summary.xlsx
+++ b/results/final_0624_summary/scene_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,80 +456,260 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>example_precision__0.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>f1__0.0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1__0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f1__0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1__0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.3</t>
         </is>
@@ -563,80 +743,260 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.6434±0.0163</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5715±0.0143</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.4324±0.0202</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.2779±0.0122</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.8684±0.0058</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.9030±0.0090</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.9463±0.0107</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.9629±0.0071</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.6826±0.0134</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.6348±0.0110</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.5350±0.0179</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.4076±0.0118</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.7412±0.0145</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.6830±0.0137</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5737±0.0209</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.4217±0.0160</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6266±0.0152</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5585±0.0120</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.4260±0.0202</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.2765±0.0120</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.5421±0.0146</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5018±0.0111</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.4402±0.0137</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.3716±0.0071</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4003±0.0161</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.3507±0.0106</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.2889±0.0113</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.2314±0.0055</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.8642±0.0073</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.8999±0.0104</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.9418±0.0107</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.9600±0.0086</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.2985±0.0197</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.3698±0.0312</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.5281±0.0311</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.7312±0.0349</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5422±0.0140</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5020±0.0110</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.4408±0.0136</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.3724±0.0074</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.3972±0.0149</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.3494±0.0107</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.2882±0.0113</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.2311±0.0056</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.8549±0.0058</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.8917±0.0101</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9373±0.0107</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9582±0.0086</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.5098±0.0170</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.4005±0.0151</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.2083±0.0236</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.0386±0.0098</t>
         </is>
@@ -670,80 +1030,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.6410±0.0166</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.5686±0.0148</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.4290±0.0196</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.2750±0.0118</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.8801±0.0051</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.9107±0.0079</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.9480±0.0117</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.9639±0.0074</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.6842±0.0137</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.6347±0.0115</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.5329±0.0177</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.4053±0.0115</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.7406±0.0141</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6817±0.0138</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.5717±0.0204</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0.4192±0.0161</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6251±0.0151</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.5561±0.0129</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.4229±0.0196</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.2737±0.0116</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.5449±0.0141</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.5028±0.0111</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.4395±0.0138</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.3708±0.0070</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.4003±0.0152</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.3504±0.0106</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.2880±0.0113</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.2307±0.0055</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.8751±0.0050</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.9071±0.0089</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.9435±0.0117</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.9610±0.0086</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.3075±0.0176</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.3722±0.0283</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>0.5296±0.0307</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.7346±0.0358</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.5449±0.0137</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.5031±0.0111</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.4401±0.0137</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.3717±0.0074</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.3976±0.0145</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.3493±0.0107</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.2874±0.0112</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.2305±0.0056</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.8665±0.0024</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.8994±0.0087</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9392±0.0120</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9592±0.0088</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.5006±0.0169</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.3932±0.0177</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.2036±0.0222</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.0353±0.0095</t>
         </is>
@@ -777,80 +1317,260 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.6428±0.0158</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.5712±0.0139</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.4320±0.0203</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.2777±0.0121</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.8657±0.0043</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.9015±0.0087</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.9457±0.0111</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.9631±0.0071</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.6813±0.0128</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.6341±0.0107</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.5346±0.0180</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.4075±0.0117</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.7397±0.0139</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.6824±0.0139</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.5734±0.0209</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.4216±0.0159</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.6258±0.0147</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5581±0.0116</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.4256±0.0203</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.2763±0.0119</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.5399±0.0136</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.5008±0.0111</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.4399±0.0137</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.3716±0.0070</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.3984±0.0152</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.3500±0.0107</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.2886±0.0114</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.2314±0.0055</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.8619±0.0063</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.8984±0.0106</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.9412±0.0111</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.9602±0.0086</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.3015±0.0208</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.3703±0.0313</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>0.5284±0.0311</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>0.7326±0.0354</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5399±0.0132</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5010±0.0110</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.4404±0.0137</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.3725±0.0074</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.3953±0.0142</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.3487±0.0108</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.2880±0.0113</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.2312±0.0055</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.8522±0.0050</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.8901±0.0100</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9367±0.0111</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9584±0.0086</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.5102±0.0165</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.4009±0.0152</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>0.2079±0.0239</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.0380±0.0100</t>
         </is>
@@ -884,80 +1604,260 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.6405±0.0165</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.5685±0.0147</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.4288±0.0196</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.2750±0.0118</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.8784±0.0058</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.9105±0.0077</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.9476±0.0120</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.9639±0.0074</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.6834±0.0135</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.6346±0.0113</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.5327±0.0177</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.4052±0.0115</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.7396±0.0135</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.6815±0.0138</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.5714±0.0204</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.4191±0.0162</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.6246±0.0149</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.5561±0.0127</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.4228±0.0196</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.2736±0.0117</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.5434±0.0133</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.5026±0.0111</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.4392±0.0138</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.3708±0.0071</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.3990±0.0144</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.3502±0.0106</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.2878±0.0113</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.2307±0.0055</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.8736±0.0046</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.9068±0.0089</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.9431±0.0120</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.9610±0.0086</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.3085±0.0173</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.3722±0.0289</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>0.5293±0.0307</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.7351±0.0360</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.5435±0.0129</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.5028±0.0111</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.4398±0.0137</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.3716±0.0074</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.3964±0.0138</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.3491±0.0107</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.2872±0.0112</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.2305±0.0056</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.8650±0.0033</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.8992±0.0086</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9388±0.0123</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9592±0.0088</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.5006±0.0169</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.3932±0.0177</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>0.2036±0.0222</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.0353±0.0095</t>
         </is>
@@ -991,80 +1891,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.6528±0.0167</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.6394±0.0187</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.6025±0.0238</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.5277±0.0202</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.8622±0.0088</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.8728±0.0129</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.8766±0.0087</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.8663±0.0099</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.6880±0.0143</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.6815±0.0142</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.6583±0.0181</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.6079±0.0169</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.7499±0.0150</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.7448±0.0143</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.7361±0.0165</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.7167±0.0190</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.6335±0.0155</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.6212±0.0166</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5858±0.0217</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.5160±0.0183</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.5480±0.0165</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.5463±0.0135</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.5391±0.0162</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.5192±0.0171</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.4090±0.0175</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.4037±0.0143</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.3942±0.0177</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.3741±0.0174</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.8563±0.0114</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.8682±0.0127</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.8720±0.0092</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.8614±0.0108</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.2871±0.0379</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.2789±0.0276</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.2791±0.0351</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>0.2975±0.0474</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.5482±0.0159</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.5465±0.0134</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.5395±0.0160</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.5193±0.0169</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.4056±0.0164</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.4012±0.0145</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.3929±0.0177</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.3735±0.0173</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.8464±0.0100</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.8578±0.0117</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.8621±0.0090</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8532±0.0095</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.5177±0.0152</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.4917±0.0220</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>0.4252±0.0307</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.3054±0.0205</t>
         </is>
@@ -1098,80 +2178,260 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.6492±0.0167</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.6335±0.0188</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.5779±0.0197</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.4617±0.0185</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.8751±0.0087</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.8896±0.0129</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.8953±0.0091</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.8934±0.0088</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.6902±0.0139</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.6832±0.0146</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.6478±0.0158</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.5680±0.0164</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.7488±0.0147</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.7437±0.0151</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.7276±0.0141</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.6847±0.0175</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.6326±0.0146</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.6182±0.0167</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.5654±0.0187</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.4540±0.0181</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.5510±0.0157</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.5506±0.0145</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.5371±0.0141</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.5012±0.0155</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.4084±0.0167</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.4038±0.0151</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.3873±0.0142</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.3507±0.0144</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.8696±0.0090</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.8853±0.0117</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.8912±0.0088</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.8883±0.0089</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.2925±0.0277</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.2853±0.0282</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>0.3013±0.0382</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.3476±0.0340</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.5514±0.0150</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.5508±0.0145</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.5375±0.0138</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.5008±0.0150</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.4057±0.0158</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.4018±0.0153</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.3864±0.0144</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.3498±0.0140</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.8611±0.0076</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.8766±0.0115</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.8834±0.0089</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8822±0.0088</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.5089±0.0147</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>0.4765±0.0207</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>0.3799±0.0254</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.1917±0.0208</t>
         </is>
@@ -1205,80 +2465,260 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0.6528±0.0174</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.6391±0.0188</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.6026±0.0223</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.5281±0.0206</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.8595±0.0077</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.8687±0.0142</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.8716±0.0109</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.8614±0.0106</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.6866±0.0147</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.6797±0.0144</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.6567±0.0172</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.6067±0.0168</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.7493±0.0152</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.7436±0.0142</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.7350±0.0154</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.7162±0.0189</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.6320±0.0160</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.6199±0.0166</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5850±0.0200</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.5159±0.0184</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.5463±0.0165</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.5437±0.0134</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.5362±0.0153</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.5171±0.0167</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.4080±0.0178</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.4020±0.0142</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.3925±0.0166</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.3730±0.0172</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.8526±0.0096</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.8635±0.0141</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.8659±0.0118</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.8565±0.0115</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>0.2836±0.0360</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.2783±0.0293</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.2772±0.0323</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>0.2965±0.0482</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.5465±0.0157</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.5439±0.0134</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.5366±0.0151</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.5173±0.0164</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4046±0.0165</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.3994±0.0143</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3910±0.0165</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.3725±0.0171</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.8425±0.0078</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.8530±0.0132</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.8559±0.0115</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8479±0.0103</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.5164±0.0163</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>0.4915±0.0216</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>0.4271±0.0270</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.3072±0.0213</t>
         </is>
@@ -1312,80 +2752,260 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.6487±0.0168</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.6327±0.0181</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.5762±0.0203</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.4621±0.0171</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.8728±0.0091</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8907±0.0119</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.8950±0.0103</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.8933±0.0101</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.6892±0.0140</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.6829±0.0137</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.6464±0.0165</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.5681±0.0158</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.7482±0.0148</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.7431±0.0147</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.7260±0.0145</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.6844±0.0176</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.6317±0.0145</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.6175±0.0161</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.5638±0.0193</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.4544±0.0169</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.5497±0.0160</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.5504±0.0135</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.5357±0.0145</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.5009±0.0157</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.4075±0.0168</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.4034±0.0143</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.3859±0.0147</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.3504±0.0144</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.8670±0.0095</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.8863±0.0107</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.8912±0.0102</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.8883±0.0102</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.2920±0.0260</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.2891±0.0290</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>0.3032±0.0391</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>0.3494±0.0326</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.5500±0.0154</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.5504±0.0135</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.5360±0.0143</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.5005±0.0151</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.4048±0.0159</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.4012±0.0146</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.3850±0.0149</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.3495±0.0141</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.8584±0.0080</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.8775±0.0108</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.8832±0.0104</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8820±0.0104</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.5081±0.0143</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>0.4751±0.0205</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>0.3783±0.0254</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.1928±0.0181</t>
         </is>
@@ -1419,80 +3039,260 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.6228±0.0154</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.6175±0.0127</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.6057±0.0254</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.5574±0.0178</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.6075±0.0142</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.6058±0.0134</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.6038±0.0254</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.5941±0.0216</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.6108±0.0141</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>0.6065±0.0121</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.5983±0.0250</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>0.5629±0.0184</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0.9163±0.0028</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.9137±0.0026</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.9076±0.0047</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.8825±0.0046</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.6021±0.0134</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.5962±0.0110</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.5857±0.0246</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.5385±0.0174</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.7160±0.0120</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.7088±0.0102</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.6955±0.0196</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.6422±0.0150</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.9003±0.0164</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.8812±0.0139</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.8435±0.0228</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.7094±0.0202</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.6122±0.0162</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.6116±0.0122</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.6075±0.0250</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.5974±0.0210</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>0.6268±0.0352</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>0.6455±0.0354</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>0.6210±0.0508</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>0.5833±0.0525</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.7174±0.0109</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.7106±0.0100</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.6950±0.0189</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.6388±0.0128</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.9064±0.0180</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.8881±0.0163</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.8493±0.0241</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.7114±0.0243</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.5938±0.0127</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.5924±0.0113</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.5888±0.0251</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.5807±0.0218</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.5762±0.0112</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>0.5656±0.0085</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>0.5482±0.0240</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.4678±0.0155</t>
         </is>
@@ -1526,80 +3326,260 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>0.6456±0.0238</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.6250±0.0219</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.5964±0.0183</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.5516±0.0318</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.6266±0.0246</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.6126±0.0224</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.5930±0.0182</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.5880±0.0344</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>0.6322±0.0242</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.6138±0.0216</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.5882±0.0175</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.5574±0.0312</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.9176±0.0044</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.9146±0.0042</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.9062±0.0035</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.8839±0.0072</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.6246±0.0243</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.6037±0.0210</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.5755±0.0165</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.5336±0.0288</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.7281±0.0190</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.7138±0.0167</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.6885±0.0151</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.6422±0.0253</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0.8910±0.0109</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.8818±0.0186</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.8441±0.0182</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.7177±0.0290</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.6293±0.0283</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.6183±0.0233</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.5979±0.0209</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.5909±0.0343</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>0.6131±0.0252</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.6379±0.0292</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>0.6434±0.0555</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.5621±0.0713</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.7261±0.0180</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.7148±0.0165</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.6886±0.0136</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.6389±0.0237</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.8956±0.0092</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.8887±0.0197</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.8493±0.0198</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.7219±0.0323</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.6109±0.0237</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.5983±0.0219</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.5795±0.0192</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.5747±0.0356</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.6016±0.0246</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0.5735±0.0194</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>0.5376±0.0147</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.4643±0.0268</t>
         </is>
@@ -1633,82 +3613,1123 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>0.1687±0.0182</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.2731±0.0222</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.2995±0.0212</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.2455±0.0295</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.1606±0.0176</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.2617±0.0206</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.2874±0.0202</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.2372±0.0291</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>0.1633±0.0178</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>0.2654±0.0211</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.2913±0.0204</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>0.2398±0.0291</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>0.8491±0.0032</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.8656±0.0035</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0.8698±0.0031</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.8606±0.0050</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.1606±0.0176</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.2616±0.0206</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.2870±0.0199</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.2367±0.0289</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.2598±0.0231</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.3832±0.0238</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.4153±0.0211</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.3574±0.0337</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.7990±0.1231</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.9314±0.0628</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.9392±0.0548</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.9375±0.0493</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.1692±0.0176</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.2720±0.0191</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.2992±0.0187</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.2430±0.0267</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>0.9983±0.0034</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>0.9819±0.0145</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>0.9720±0.0151</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>0.9593±0.0216</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.2721±0.0263</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.4046±0.0254</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.4344±0.0235</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.3707±0.0367</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.9947±0.0066</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>0.9764±0.0110</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.9739±0.0082</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.9620±0.0176</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.1578±0.0174</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0.2555±0.0201</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0.2798±0.0196</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.2302±0.0278</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
         <is>
           <t>0.1525±0.0170</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>0.2501±0.0192</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>0.2744±0.0190</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.2275±0.0280</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.3765±0.0159</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.3785±0.0192</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.3662±0.0163</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.3546±0.0372</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.6246±0.0174</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.6188±0.0161</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.6178±0.0179</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.5899±0.0325</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.6073±0.0135</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.6030±0.0151</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.6117±0.0156</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.6054±0.0364</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.6121±0.0155</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.6064±0.0151</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.6088±0.0162</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.5883±0.0334</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.9157±0.0034</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.9153±0.0029</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.9127±0.0037</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.8993±0.0055</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.6043±0.0158</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.5975±0.0146</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.5971±0.0158</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.5702±0.0322</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.7150±0.0131</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.7112±0.0123</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.7082±0.0140</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.6751±0.0273</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.8983±0.0097</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.8996±0.0134</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.8712±0.0206</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.7885±0.0259</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.6097±0.0161</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.6079±0.0181</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.6151±0.0160</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.6115±0.0334</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>0.6198±0.0245</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>0.6431±0.0200</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>0.6380±0.0532</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.6434±0.0800</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.7155±0.0134</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.7133±0.0119</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.7100±0.0128</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.6772±0.0224</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.9037±0.0118</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.9051±0.0144</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.8763±0.0216</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.7946±0.0275</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.5923±0.0149</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.5888±0.0163</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.5969±0.0132</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.5915±0.0341</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.5812±0.0169</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.5706±0.0140</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.5625±0.0152</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.5174±0.0299</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.1987±0.0174</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.2076±0.0159</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.2522±0.0333</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.3065±0.0445</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.7975±0.0197</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.7779±0.0221</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.6703±0.0349</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.4594±0.0397</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.7664±0.0196</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.7529±0.0200</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.6847±0.0330</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.5678±0.0427</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.7767±0.0196</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.7597±0.0208</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.6673±0.0330</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.4884±0.0389</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.9206±0.0063</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.9151±0.0073</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.8872±0.0074</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.8188±0.0089</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.7662±0.0197</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.7482±0.0206</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.6468±0.0329</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.4441±0.0381</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.7786±0.0181</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.7652±0.0211</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.6893±0.0226</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.5277±0.0300</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.8044±0.0195</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.7881±0.0225</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.7060±0.0210</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.5018±0.0275</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.7597±0.0214</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.7465±0.0203</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.6815±0.0331</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.5687±0.0399</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>0.4077±0.0396</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>0.3806±0.0440</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.4419±0.0956</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.5142±0.1013</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.7708±0.0181</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.7557±0.0205</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.6799±0.0232</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.5237±0.0263</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.7979±0.0196</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.7795±0.0240</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.6908±0.0216</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.4947±0.0225</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.7454±0.0170</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.7333±0.0181</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.6700±0.0318</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.5573±0.0385</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.7349±0.0199</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.7140±0.0201</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.5868±0.0353</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.3205±0.0414</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.2461±0.0281</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.2611±0.0248</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.2870±0.0371</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.2365±0.0537</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.7173±0.0231</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.6792±0.0175</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.5873±0.0238</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.4408±0.0355</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.7178±0.0267</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.6931±0.0214</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.6415±0.0324</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.6093±0.0435</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.7088±0.0240</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.6754±0.0178</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.5983±0.0254</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.4873±0.0339</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.9136±0.0038</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.8997±0.0044</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0.8734±0.0062</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.7949±0.0162</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.6909±0.0221</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.6537±0.0168</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.5669±0.0227</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.4257±0.0336</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.7483±0.0140</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.7134±0.0120</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.6474±0.0211</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.5144±0.0258</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.7970±0.0182</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.7537±0.0222</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.6704±0.0286</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.4612±0.0355</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.7139±0.0249</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.6882±0.0217</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.6382±0.0311</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.6051±0.0425</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>0.4537±0.0235</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>0.4425±0.0648</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>0.4912±0.0933</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.4763±0.0602</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.7433±0.0125</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.7077±0.0124</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.6408±0.0184</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.5114±0.0252</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.7941±0.0206</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.7409±0.0235</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>0.6518±0.0243</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.4477±0.0294</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.6994±0.0235</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.6782±0.0215</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>0.6316±0.0317</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.5995±0.0418</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.6377±0.0180</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.5893±0.0178</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4759±0.0226</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.2599±0.0428</t>
         </is>
       </c>
     </row>
